--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513263_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513263_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8955</v>
+        <v>7.6895</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9258</v>
+        <v>7.5757</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0303</v>
+        <v>0.1138</v>
       </c>
       <c r="G2" t="n">
         <v>6.4236</v>
@@ -610,13 +610,13 @@
         <v>1.1014</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3739</v>
+        <v>-0.5799</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7046</v>
+        <v>-0.0547</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6693</v>
+        <v>-0.5252</v>
       </c>
       <c r="V2" t="n">
         <v>0.7444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0454</v>
+        <v>2.6139</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0941</v>
+        <v>1.8067</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9513</v>
+        <v>0.8072</v>
       </c>
       <c r="G3" t="n">
         <v>3.2539</v>
@@ -688,13 +688,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.232</v>
+        <v>-0.1995</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3327</v>
+        <v>0.0453</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1007</v>
+        <v>-0.2448</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0534</v>
+        <v>2.3742</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8554</v>
+        <v>3.0897</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.802</v>
+        <v>-0.7155</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7022</v>
@@ -766,13 +766,13 @@
         <v>2.6433</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7686</v>
+        <v>-1.4478</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9327</v>
+        <v>-0.6984</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8359</v>
+        <v>-0.7494</v>
       </c>
       <c r="V4" t="n">
         <v>2.9823</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8119</v>
+        <v>0.8164</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0565</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8153</v>
+        <v>0.8729</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4475</v>
@@ -844,13 +844,13 @@
         <v>2.6433</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7583</v>
+        <v>-0.7538</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4079</v>
+        <v>-0.461</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3505</v>
+        <v>-0.2928</v>
       </c>
       <c r="V5" t="n">
         <v>0.3745</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2271</v>
+        <v>0.4519</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9908</v>
+        <v>0.2182</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7637</v>
+        <v>0.2337</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.783</v>
+        <v>2.175</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1797</v>
+        <v>-0.3028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6032</v>
+        <v>2.4778</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.2544</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.877</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.783</v>
+        <v>-0.0794</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1797</v>
+        <v>-0.6802</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6032</v>
+        <v>0.6008</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1014</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1089</v>
+        <v>-0.4147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1281</v>
+        <v>-0.186</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0192</v>
+        <v>-0.2288</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1189</v>
+        <v>-1.3084</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1189</v>
+        <v>-0.7489</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0959</v>
+        <v>0.3199</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08019999999999999</v>
+        <v>1.0549</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1761</v>
+        <v>-0.7349</v>
       </c>
       <c r="G7" t="n">
-        <v>2.175</v>
+        <v>-0.783</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3028</v>
+        <v>-0.1797</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4778</v>
+        <v>-0.6032</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2544</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.877</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0794</v>
+        <v>-0.783</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6802</v>
+        <v>-0.1797</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6008</v>
+        <v>-0.6032</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1014</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7708</v>
+        <v>-0.016</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4843</v>
+        <v>-0.0641</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2864</v>
+        <v>0.048</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3084</v>
+        <v>1.1189</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7489</v>
+        <v>1.1189</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1721</v>
+        <v>0.0091</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0817</v>
+        <v>-0.9004</v>
       </c>
       <c r="F8" t="n">
         <v>0.9095</v>
@@ -1078,10 +1078,10 @@
         <v>1.7622</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9935</v>
+        <v>-0.8123</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5765</v>
+        <v>-0.3953</v>
       </c>
       <c r="U8" t="n">
         <v>-0.417</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>P. ALI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1775</v>
+        <v>-0.4251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5646</v>
+        <v>-1.0169</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7421</v>
+        <v>0.5918</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3764</v>
+        <v>0.3897</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2884</v>
+        <v>-1.1585</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>1.5482</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7625</v>
+        <v>1.0305</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2905</v>
+        <v>-0.7437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.472</v>
+        <v>1.7741</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1389</v>
+        <v>-0.6407</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5789</v>
+        <v>-0.4148</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.2259</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4405</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5419</v>
+        <v>2.8635</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6967</v>
+        <v>-0.5417</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2824</v>
+        <v>-0.5891</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4143</v>
+        <v>0.0474</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9384</v>
+        <v>-0.9339</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3789</v>
+        <v>0.7444</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5595</v>
+        <v>-1.6784</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ALI</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5225</v>
+        <v>-0.9286</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0278</v>
+        <v>-1.4048</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5053</v>
+        <v>0.4762</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3897</v>
+        <v>-2.6438</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1585</v>
+        <v>-0.4327</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5482</v>
+        <v>-2.2111</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0305</v>
+        <v>-0.7736</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7437</v>
+        <v>0.8102</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7741</v>
+        <v>-1.5838</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6407</v>
+        <v>-1.8702</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4148</v>
+        <v>-1.2429</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2259</v>
+        <v>-0.6273</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6608000000000001</v>
+        <v>2.2027</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8635</v>
+        <v>2.2027</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6391</v>
+        <v>-1.2365</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6</v>
+        <v>-0.6312</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0391</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9339</v>
+        <v>0.7489</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7444</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6784</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6361</v>
+        <v>-1.6598</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0547</v>
+        <v>-0.543</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4185</v>
+        <v>-1.1169</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6438</v>
+        <v>-1.3764</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4327</v>
+        <v>-1.2884</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2111</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7736</v>
+        <v>0.7625</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8102</v>
+        <v>0.2905</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5838</v>
+        <v>0.472</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8702</v>
+        <v>-2.1389</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2429</v>
+        <v>-1.5789</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6273</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2027</v>
+        <v>0.4405</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2027</v>
+        <v>1.5419</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.944</v>
+        <v>0.2144</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2811</v>
+        <v>0.1748</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6629</v>
+        <v>0.0395</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7489</v>
+        <v>-0.9384</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3789</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7489</v>
+        <v>-0.5595</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.621</v>
+        <v>11.2614</v>
       </c>
       <c r="E12" t="n">
-        <v>9.1829</v>
+        <v>9.823600000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4379</v>
+        <v>1.4378</v>
       </c>
       <c r="G12" t="n">
         <v>6.5688</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2581</v>
+        <v>-4.258100000000001</v>
       </c>
       <c r="I12" t="n">
         <v>10.8269</v>
@@ -1375,7 +1375,7 @@
         <v>-9.176499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.818499999999999</v>
+        <v>-7.8185</v>
       </c>
       <c r="O12" t="n">
         <v>-1.358</v>
@@ -1390,13 +1390,13 @@
         <v>16.5205</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.4284</v>
+        <v>-5.7878</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5001</v>
+        <v>-2.8597</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.9283</v>
+        <v>-2.9284</v>
       </c>
       <c r="V12" t="n">
         <v>1.669399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9567</v>
+        <v>4.6177</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8106</v>
+        <v>5.9904</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8539</v>
+        <v>-1.3727</v>
       </c>
       <c r="G13" t="n">
         <v>0.481</v>
@@ -1468,13 +1468,13 @@
         <v>1.1014</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3974</v>
+        <v>1.0584</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0621</v>
+        <v>0.242</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3352</v>
+        <v>0.8164</v>
       </c>
       <c r="V13" t="n">
         <v>1.977</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8633</v>
+        <v>4.1423</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5049</v>
+        <v>1.9736</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3584</v>
+        <v>2.1687</v>
       </c>
       <c r="G14" t="n">
         <v>2.8196</v>
@@ -1546,13 +1546,13 @@
         <v>0.4405</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7662</v>
+        <v>1.0452</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2</v>
+        <v>0.2686</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.7765</v>
       </c>
       <c r="V14" t="n">
         <v>0.9384</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9066</v>
+        <v>1.9707</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2201</v>
+        <v>1.8687</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3136</v>
+        <v>0.1021</v>
       </c>
       <c r="G15" t="n">
         <v>1.5035</v>
@@ -1624,13 +1624,13 @@
         <v>0.8811</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5697</v>
+        <v>0.6339</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7935</v>
+        <v>0.442</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2238</v>
+        <v>0.1918</v>
       </c>
       <c r="V15" t="n">
         <v>1.155</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3435</v>
+        <v>0.7033</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5367</v>
+        <v>0.6539</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1932</v>
+        <v>0.0495</v>
       </c>
       <c r="G16" t="n">
         <v>0.0168</v>
@@ -1702,13 +1702,13 @@
         <v>1.1014</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4341</v>
+        <v>0.794</v>
       </c>
       <c r="T16" t="n">
-        <v>0.517</v>
+        <v>0.6342</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0829</v>
+        <v>0.1598</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1074</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6711</v>
+        <v>-1.0802</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1257</v>
+        <v>-0.4772</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5454</v>
+        <v>-0.6031</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6073</v>
@@ -1858,13 +1858,13 @@
         <v>0.2203</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7159</v>
+        <v>1.3068</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4262</v>
+        <v>1.0747</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2897</v>
+        <v>0.232</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0667</v>
+        <v>-1.7845</v>
       </c>
       <c r="E19" t="n">
-        <v>0.501</v>
+        <v>-1.4374</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5678</v>
+        <v>-0.3472</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3046</v>
+        <v>0.5411</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1157</v>
+        <v>1.2539</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1889</v>
+        <v>-0.7128</v>
       </c>
       <c r="J19" t="n">
-        <v>0.873</v>
+        <v>1.6402</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1894</v>
+        <v>1.1682</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6835</v>
+        <v>0.472</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1775</v>
+        <v>-1.0992</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3051</v>
+        <v>0.0857</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8724</v>
+        <v>-1.1848</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-2.6433</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1014</v>
+        <v>-3.3041</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4405</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1665</v>
+        <v>0.5026</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7294</v>
+        <v>0.2265</v>
       </c>
       <c r="U19" t="n">
-        <v>0.437</v>
+        <v>0.2762</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2678</v>
+        <v>-0.185</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2678</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2783</v>
+        <v>-2.1185</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6717</v>
+        <v>-1.4081</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6066</v>
+        <v>-0.7104</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5411</v>
+        <v>-2.2568</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2539</v>
+        <v>-0.1673</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7128</v>
+        <v>-2.0895</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6402</v>
+        <v>-1.4503</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1682</v>
+        <v>0.0359</v>
       </c>
       <c r="L20" t="n">
-        <v>0.472</v>
+        <v>-1.4862</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0992</v>
+        <v>-0.8065</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0857</v>
+        <v>-0.2032</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1848</v>
+        <v>-0.6032</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.6433</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.3041</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6608000000000001</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0089</v>
+        <v>0.1382</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0078</v>
+        <v>0.0422</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0167</v>
+        <v>0.0961</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.185</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4105</v>
+        <v>-2.5642</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6424</v>
+        <v>0.0324</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.768</v>
+        <v>-2.5966</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2568</v>
+        <v>-1.3046</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1673</v>
+        <v>-1.1157</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0895</v>
+        <v>-0.1889</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4503</v>
+        <v>0.873</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0359</v>
+        <v>0.1894</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4862</v>
+        <v>0.6835</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8065</v>
+        <v>-2.1775</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2032</v>
+        <v>-1.3051</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6032</v>
+        <v>-0.8724</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.4405</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1537</v>
+        <v>0.669</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1922</v>
+        <v>0.2608</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0384</v>
+        <v>0.4082</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2678</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2678</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6542</v>
+        <v>-3.3371</v>
       </c>
       <c r="E22" t="n">
         <v>-1.0522</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6021</v>
+        <v>-2.285</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8877</v>
@@ -2170,13 +2170,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1957</v>
+        <v>0.5128</v>
       </c>
       <c r="T22" t="n">
         <v>0.0046</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1911</v>
+        <v>0.5082</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4203</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7325</v>
+        <v>-5.2266</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9663</v>
+        <v>-2.8853</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7662</v>
+        <v>-2.3414</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5494</v>
+        <v>-1.5946</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5323</v>
+        <v>-0.1161</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0172</v>
+        <v>-1.4785</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5465</v>
+        <v>-0.5309</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5309</v>
+        <v>0.2987</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0774</v>
+        <v>-0.8296</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0029</v>
+        <v>-1.0637</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0632</v>
+        <v>-0.4148</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9397</v>
+        <v>-0.6489</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9825</v>
+        <v>-1.3216</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.3041</v>
+        <v>-2.2027</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3216</v>
+        <v>0.8811</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0601</v>
+        <v>0.1882</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1157</v>
+        <v>-0.1516</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1758</v>
+        <v>0.3399</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2608</v>
+        <v>-2.4986</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2608</v>
+        <v>-2.4986</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1472</v>
+        <v>-5.4322</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8226</v>
+        <v>-4.9663</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3246</v>
+        <v>-0.4659</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5946</v>
+        <v>-3.5494</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1161</v>
+        <v>-0.5323</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4785</v>
+        <v>-3.0172</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5309</v>
+        <v>-1.5465</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2987</v>
+        <v>0.5309</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8296</v>
+        <v>-2.0774</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0637</v>
+        <v>-2.0029</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4148</v>
+        <v>-1.0632</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6489</v>
+        <v>-0.9397</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3216</v>
+        <v>-1.9825</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2027</v>
+        <v>-3.3041</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8811</v>
+        <v>1.3216</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7323</v>
+        <v>0.3605</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0889</v>
+        <v>-0.1157</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3566</v>
+        <v>0.4762</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4986</v>
+        <v>-0.2608</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4986</v>
+        <v>-0.2608</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.6208</v>
+        <v>-9.839700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.438</v>
+        <v>-1.437899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.183</v>
+        <v>-8.402000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-6.5688</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2579</v>
+        <v>4.257899999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-10.8271</v>
@@ -2380,16 +2380,16 @@
         <v>9.176499999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8184</v>
+        <v>7.818400000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.357899999999999</v>
+        <v>1.3579</v>
       </c>
       <c r="M25" t="n">
         <v>-15.7455</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.5605</v>
+        <v>-3.560499999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-12.1849</v>
@@ -2404,13 +2404,13 @@
         <v>7.7095</v>
       </c>
       <c r="S25" t="n">
-        <v>6.428500000000001</v>
+        <v>7.209600000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9282</v>
+        <v>2.9283</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5</v>
+        <v>4.2813</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6695</v>
